--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
   <si>
     <t>Filename</t>
   </si>
@@ -808,697 +808,685 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9955,0.0012,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9590,0.0006,0.0002,0.0171</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9907,0.0022,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.9733,0.0002,0.0017,0.0124</t>
+  </si>
+  <si>
+    <t>0.0873,0.0002,0.0000,0.9799</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3349,0.0053,0.5662,0.0012</t>
+  </si>
+  <si>
+    <t>0.0008,0.0006,0.9988,0.0002</t>
+  </si>
+  <si>
+    <t>0.0729,0.0002,0.9752,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.8802,0.0004,0.1458,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9977,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.9924,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9990,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.2867,0.0005,0.7368,0.0009</t>
+  </si>
+  <si>
+    <t>0.4087,0.0003,0.6941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9957,0.0004</t>
+  </si>
+  <si>
+    <t>0.0081,0.0002,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.0001,0.9938,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0220,0.9691,0.0039,0.0025</t>
+  </si>
+  <si>
+    <t>0.6410,0.0542,0.1372,0.0013</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.9992,0.0167</t>
+  </si>
+  <si>
+    <t>0.0049,0.9523,0.0816,0.0005</t>
+  </si>
+  <si>
+    <t>0.9754,0.0205,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.9235,0.0281,0.0256,0.0026</t>
+  </si>
+  <si>
+    <t>0.2166,0.7827,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9921,0.4255,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.2659,0.6774,0.0031</t>
+  </si>
+  <si>
+    <t>0.0207,0.0004,0.9766,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.0022,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0055,0.0000,0.9934,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0180,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.9921,0.0070,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9638,0.0002,0.8794</t>
+  </si>
+  <si>
+    <t>0.0016,0.9960,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.9977,0.0038,0.0010</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.0227,0.9859,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0013,0.9961,0.0005</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9861,0.0110,0.0027,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9997,0.0018</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9117,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0008,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9995,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9634,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0000,0.0065,0.0000</t>
+  </si>
+  <si>
+    <t>0.9930,0.0007,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,0.9999,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.7927,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9254,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.0596,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.7739,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.0009,0.9989</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0002,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0047,0.9983</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.0005,0.9993</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0003,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9966,0.9637,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9940,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9500,0.9423,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0042,0.9980,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9104,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9812,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9678,0.0005,0.0187,0.0010</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9993,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0005,0.0122,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.0001,0.9953,0.0001</t>
-  </si>
-  <si>
-    <t>0.7902,0.0033,0.1417,0.0005</t>
+    <t>0.9981,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9958,0.0030,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9857,0.0004,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9992,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0194,0.9838,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9985,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8006,0.0002,0.2634,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0006,0.9857,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.0003,0.9901,0.0004</t>
+    <t>0.0002,0.9995,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9978,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1973,0.8602,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.1237,0.0221,0.7305,0.0041</t>
+  </si>
+  <si>
+    <t>0.9880,0.0003,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.9854,0.0042,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.3351,0.0054,0.5475,0.0018</t>
+  </si>
+  <si>
+    <t>0.0021,0.0014,0.0335,0.9875</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9597,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8396,0.1574,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.4241,0.6114,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7400,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.1916,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.9809,0.0007,0.0093,0.0002</t>
+  </si>
+  <si>
+    <t>0.0694,0.0026,0.9334,0.0011</t>
+  </si>
+  <si>
+    <t>0.0071,0.0012,0.9924,0.0009</t>
+  </si>
+  <si>
+    <t>0.8725,0.0004,0.1701,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.0001,0.0001,0.9975</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.8792,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.6323,0.4350,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7706,0.3066,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.4423,0.0004,0.0037,0.6961</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9980,0.0048</t>
+  </si>
+  <si>
+    <t>0.9935,0.0003,0.0062,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0005,0.0031,0.0005</t>
+  </si>
+  <si>
+    <t>0.0059,0.9896,0.0016,0.0011</t>
+  </si>
+  <si>
+    <t>0.8943,0.0128,0.0557,0.0007</t>
+  </si>
+  <si>
+    <t>0.9915,0.0002,0.0089,0.0001</t>
+  </si>
+  <si>
+    <t>0.9792,0.0060,0.0060,0.0005</t>
+  </si>
+  <si>
+    <t>0.9918,0.0019,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9347,0.0528,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0008,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9204,0.1030,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.1414,0.8866,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.9713,0.0326,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.6105,0.0156,0.3979,0.0003</t>
+  </si>
+  <si>
+    <t>0.9519,0.0707,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9978,0.0012,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9867,0.0125,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0018,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0028,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.2877,0.9953,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0316,0.9976,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0055,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.0000,0.9996,0.0002</t>
   </si>
   <si>
-    <t>0.2561,0.7261,0.0035,0.0017</t>
-  </si>
-  <si>
-    <t>0.9904,0.0098,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9996,0.0059</t>
-  </si>
-  <si>
-    <t>0.0003,0.9770,0.4924,0.0003</t>
-  </si>
-  <si>
-    <t>0.7074,0.0271,0.1401,0.0018</t>
-  </si>
-  <si>
-    <t>0.9966,0.0027,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5249,0.5564,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.9924,0.0244,0.0002</t>
-  </si>
-  <si>
-    <t>0.0206,0.3373,0.3933,0.0026</t>
-  </si>
-  <si>
-    <t>0.0018,0.0010,0.9943,0.0022</t>
-  </si>
-  <si>
-    <t>0.0009,0.0009,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0000,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.5819,0.9922,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9965,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0296,0.2514,0.0081,0.9150</t>
-  </si>
-  <si>
-    <t>0.0007,0.9973,0.0092,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.0242,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0031,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.9985,0.0004</t>
-  </si>
-  <si>
-    <t>0.9965,0.0034,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9892,0.0087,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0011,0.9995,0.0032</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.7246,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0006,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8853,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0002,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.7488,0.0006,0.3037,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9651,0.9960,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9302,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.5314,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9842,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0022,0.9985</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0026,0.0000,0.0014,0.9982</t>
-  </si>
-  <si>
-    <t>0.0033,0.0004,0.0007,0.9978</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0004,0.9466,0.9114,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.8614,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0911,0.9828,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9868,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9803,0.8357,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.0081,0.0020,0.9863,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0018,0.9888,0.0018</t>
+  </si>
+  <si>
+    <t>0.0074,0.0022,0.9884,0.0003</t>
+  </si>
+  <si>
+    <t>0.0092,0.0031,0.9903,0.0001</t>
+  </si>
+  <si>
+    <t>0.9694,0.0023,0.0178,0.0000</t>
+  </si>
+  <si>
+    <t>0.9954,0.0003,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0445,0.0007,0.9701,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.9940,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9958,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0762,0.9393,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9256,0.0923,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0228,0.9795,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0013,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9592,0.0001,0.0609,0.0001</t>
+  </si>
+  <si>
+    <t>0.9696,0.0013,0.0137,0.0015</t>
+  </si>
+  <si>
+    <t>0.1986,0.0044,0.8010,0.0005</t>
+  </si>
+  <si>
+    <t>0.0076,0.0059,0.9815,0.0119</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9997,0.0022</t>
+  </si>
+  <si>
+    <t>0.0006,0.0106,0.9962,0.0011</t>
+  </si>
+  <si>
+    <t>0.0017,0.0016,0.9969,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9987,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0045,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0008,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9989,0.0006,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9978,0.0018,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9962,0.0034,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0016,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0018,0.9985,0.0005</t>
-  </si>
-  <si>
-    <t>0.9748,0.0007,0.0147,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9976,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8441,0.2240,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.8089,0.0046,0.1570,0.0004</t>
-  </si>
-  <si>
-    <t>0.0782,0.0005,0.9459,0.0001</t>
-  </si>
-  <si>
-    <t>0.1067,0.3875,0.1087,0.0020</t>
-  </si>
-  <si>
-    <t>0.1500,0.0250,0.6879,0.0033</t>
-  </si>
-  <si>
-    <t>0.0092,0.0026,0.0856,0.9486</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0023</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9908,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9392,0.0370,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.8862,0.1158,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0006,0.0013,0.0002</t>
+    <t>0.9988,0.0004,0.0002,0.0002</t>
   </si>
   <si>
     <t>0.9994,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0005,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.2207,0.9960,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0370,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0036,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0014,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.9739,0.0006,0.0167,0.0005</t>
-  </si>
-  <si>
-    <t>0.7849,0.0001,0.3580,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9985,0.0002</t>
-  </si>
-  <si>
-    <t>0.1641,0.0012,0.8631,0.0006</t>
-  </si>
-  <si>
-    <t>0.0558,0.0000,0.0001,0.9867</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0027,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0018,0.0001,0.0003,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.6331,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.1133,0.9062,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9969,0.0008,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.7174,0.3066,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7226,0.0005,0.0060,0.2898</t>
-  </si>
-  <si>
-    <t>0.0008,0.0033,0.9982,0.0012</t>
-  </si>
-  <si>
-    <t>0.9955,0.0000,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.9925,0.0007,0.0039,0.0005</t>
-  </si>
-  <si>
-    <t>0.0173,0.9783,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.9343,0.0061,0.0335,0.0011</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.2740,0.6644,0.0064,0.0010</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4230,0.2154,0.0622,0.0007</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9908,0.0033,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9812,0.0139,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.0777,0.9434,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.8087,0.2639,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.3798,0.0677,0.3916,0.0008</t>
-  </si>
-  <si>
-    <t>0.9983,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0015,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.9405,0.0139,0.0301,0.0026</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0045,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.0002,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0437,0.9929,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0018,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9996,0.0006</t>
-  </si>
-  <si>
-    <t>0.0652,0.0029,0.9305,0.0003</t>
-  </si>
-  <si>
-    <t>0.0088,0.0007,0.9910,0.0005</t>
-  </si>
-  <si>
-    <t>0.0175,0.0018,0.9770,0.0007</t>
-  </si>
-  <si>
-    <t>0.1882,0.0017,0.8041,0.0002</t>
-  </si>
-  <si>
-    <t>0.1214,0.0046,0.8570,0.0001</t>
-  </si>
-  <si>
-    <t>0.8673,0.0019,0.1286,0.0000</t>
-  </si>
-  <si>
-    <t>0.9552,0.0008,0.0308,0.0008</t>
-  </si>
-  <si>
-    <t>0.0101,0.0027,0.9862,0.0004</t>
-  </si>
-  <si>
-    <t>0.7503,0.3144,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0054,0.9948,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.5971,0.4884,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9482,0.0773,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0082,0.9915,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.8270,0.0622,0.0082,0.0014</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9797,0.0013,0.0097,0.0007</t>
-  </si>
-  <si>
-    <t>0.1688,0.0050,0.8233,0.0013</t>
-  </si>
-  <si>
-    <t>0.0505,0.0023,0.9537,0.0032</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9994,0.0017</t>
-  </si>
-  <si>
-    <t>0.0007,0.0232,0.9965,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0021,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0031,0.0038,0.9898,0.0032</t>
-  </si>
-  <si>
-    <t>0.0011,0.0064,0.9918,0.0015</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9916,0.0082,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9962,0.0021,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0057,0.9966,0.0006</t>
-  </si>
-  <si>
-    <t>0.6594,0.0016,0.3556,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0564,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0003,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0042,0.9970,0.0013</t>
-  </si>
-  <si>
-    <t>0.6612,0.0003,0.4164,0.0003</t>
-  </si>
-  <si>
-    <t>0.2784,0.0001,0.8276,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9928,0.0041,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0140,0.0049,0.9683,0.0013</t>
-  </si>
-  <si>
-    <t>0.0005,0.0030,0.9975,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0009,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0006,0.9976,0.0008</t>
-  </si>
-  <si>
-    <t>0.0014,0.0014,0.9971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0003,0.9977,0.0017</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0014,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.0054,0.0004,0.0004,0.9975</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.9882,0.0004,0.0017,0.0011</t>
+    <t>0.0004,0.0010,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0336,0.0248,0.9320,0.0018</t>
+  </si>
+  <si>
+    <t>0.9933,0.0011,0.0044,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.1574,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0009,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0009,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0003,0.9964,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9977,0.0012</t>
+  </si>
+  <si>
+    <t>0.0092,0.0008,0.9857,0.0020</t>
+  </si>
+  <si>
+    <t>0.0353,0.0001,0.9758,0.0002</t>
+  </si>
+  <si>
+    <t>0.9810,0.0001,0.0211,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0038,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0019,0.9897,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0038,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0175,0.9924,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0135,0.0002,0.9734,0.0020</t>
+  </si>
+  <si>
+    <t>0.0023,0.0014,0.9952,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9974,0.0027</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.0003,0.0010,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0962,0.0003,0.0022,0.9502</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.4433,0.0013,0.0005,0.6219</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1872,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1886,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1900,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1923,10 +1911,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1928,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1982,7 +1970,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +1984,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2038,7 +2026,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,10 +2037,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2054,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,10 +2065,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2082,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2096,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2110,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2124,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2138,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2152,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2166,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2189,10 +2177,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,7 +2194,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2208,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2222,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2236,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2250,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2264,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2290,7 +2278,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,7 +2292,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2306,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2320,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2334,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,7 +2348,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2362,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2376,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2399,10 +2387,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2404,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2418,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2432,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2455,10 +2443,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2460,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2474,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,10 +2485,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2502,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2516,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2530,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2544,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2558,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2572,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2586,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2600,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2614,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2628,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2642,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2656,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2670,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2684,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2698,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2724,7 +2712,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2738,7 +2726,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2752,7 +2740,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2766,7 +2754,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2780,7 +2768,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2794,7 +2782,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2808,7 +2796,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2822,7 +2810,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,7 +2824,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2850,7 +2838,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2864,7 +2852,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2878,7 +2866,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2892,7 +2880,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2903,10 +2891,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2920,7 +2908,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2934,7 +2922,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2948,7 +2936,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2962,7 +2950,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>265</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3102,7 +3090,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3116,7 +3104,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3130,7 +3118,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>317</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3144,7 +3132,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3158,7 +3146,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3172,7 +3160,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3214,7 +3202,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3216,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3230,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3244,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3258,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3284,7 +3272,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3298,7 +3286,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3312,7 +3300,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3314,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3328,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3342,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3356,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3370,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3384,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3398,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3412,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3426,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>283</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3440,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3463,10 +3451,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3477,10 +3465,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3491,10 +3479,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3508,7 +3496,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3522,7 +3510,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,7 +3524,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3538,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3552,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>372</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3566,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3580,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3594,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3631,10 +3619,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3636,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>378</v>
+        <v>317</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3650,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3664,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3678,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3692,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3706,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3720,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3734,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3757,10 +3745,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3774,7 +3762,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3776,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3790,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3804,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3827,10 +3815,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3844,7 +3832,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3855,10 +3843,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3872,7 +3860,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3874,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3888,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3902,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3928,7 +3916,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3930,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3953,10 +3941,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3958,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +3972,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3986,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4009,10 +3997,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4014,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4028,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4042,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4056,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,7 +4070,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4084,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4098,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4121,10 +4109,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4138,7 +4126,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4140,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4154,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>350</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4168,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4182,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4196,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4210,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4224,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4238,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4252,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>417</v>
+        <v>273</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4266,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,7 +4280,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4294,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,7 +4308,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4322,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4336,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4350,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4364,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4378,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4392,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4406,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4420,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4434,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4448,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4462,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4476,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4490,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4504,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4518,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4544,7 +4532,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4558,7 +4546,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4572,7 +4560,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4586,7 +4574,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4588,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4614,7 +4602,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4625,10 +4613,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4630,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4653,10 +4641,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,7 +4658,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4672,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4686,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4700,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4714,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,7 +4728,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,7 +4742,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4756,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4770,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,7 +4784,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4798,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4812,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4826,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4840,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4854,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4868,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>273</v>
+        <v>317</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4882,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4896,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4910,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4924,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4950,7 +4938,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,7 +4952,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4978,7 +4966,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4992,7 +4980,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5006,7 +4994,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5020,7 +5008,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5034,7 +5022,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>311</v>
+        <v>467</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5048,7 +5036,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5062,7 +5050,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5064,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5078,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5101,10 +5089,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,7 +5106,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5120,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5134,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5148,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>478</v>
+        <v>271</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5162,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>479</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5176,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5190,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5204,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5218,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5232,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5246,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5260,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5286,7 +5274,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5288,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5302,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5328,7 +5316,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5342,7 +5330,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5356,7 +5344,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5370,7 +5358,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5384,7 +5372,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5398,7 +5386,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5412,7 +5400,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>393</v>
+        <v>489</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5414,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>493</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5437,10 +5425,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
